--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/RepProdIndexGz.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/RepProdIndexGz.xlsx
@@ -203,17 +203,17 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -523,16 +523,16 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="2" width="9.375" customWidth="1"/>
-    <col min="3" max="3" width="15.875" style="5" customWidth="1"/>
+    <col min="3" max="3" width="15.875" style="8" customWidth="1"/>
     <col min="4" max="6" width="13.75" customWidth="1"/>
     <col min="7" max="7" width="17.5" customWidth="1"/>
-    <col min="8" max="8" width="13.75" style="6" customWidth="1"/>
-    <col min="9" max="9" width="19.375" style="6" customWidth="1"/>
+    <col min="8" max="8" width="13.75" style="5" customWidth="1"/>
+    <col min="9" max="9" width="19.375" style="5" customWidth="1"/>
     <col min="10" max="10" width="11.875" customWidth="1"/>
     <col min="11" max="13" width="13.75" customWidth="1"/>
     <col min="14" max="14" width="17.5" customWidth="1"/>
-    <col min="15" max="15" width="13.75" style="6" customWidth="1"/>
-    <col min="16" max="16" width="19.375" style="6" customWidth="1"/>
+    <col min="15" max="15" width="13.75" style="5" customWidth="1"/>
+    <col min="16" max="16" width="19.375" style="5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="24" customHeight="1">
@@ -557,10 +557,10 @@
       <c r="G1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="6" t="s">
         <v>7</v>
       </c>
       <c r="J1" s="4" t="s">
@@ -578,10 +578,10 @@
       <c r="N1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="8" t="s">
+      <c r="O1" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="8" t="s">
+      <c r="P1" s="6" t="s">
         <v>14</v>
       </c>
     </row>

--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/RepProdIndexGz.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/RepProdIndexGz.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Git\NY\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\nyxp\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="18525" windowHeight="7125"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="18530" windowHeight="7130"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -107,7 +107,7 @@
     <t>母产品单位累计净值</t>
   </si>
   <si>
-    <t>日期(yyyy/mm/dd)*</t>
+    <t>日期(yyyy-mm-dd)*</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -209,10 +209,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -520,19 +520,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:P1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="2" width="9.375" customWidth="1"/>
-    <col min="3" max="3" width="15.875" style="8" customWidth="1"/>
-    <col min="4" max="6" width="13.75" customWidth="1"/>
-    <col min="7" max="7" width="17.5" customWidth="1"/>
-    <col min="8" max="8" width="13.75" style="5" customWidth="1"/>
-    <col min="9" max="9" width="19.375" style="5" customWidth="1"/>
-    <col min="10" max="10" width="11.875" customWidth="1"/>
-    <col min="11" max="13" width="13.75" customWidth="1"/>
-    <col min="14" max="14" width="17.5" customWidth="1"/>
-    <col min="15" max="15" width="13.75" style="5" customWidth="1"/>
-    <col min="16" max="16" width="19.375" style="5" customWidth="1"/>
+    <col min="1" max="2" width="9.36328125" customWidth="1"/>
+    <col min="3" max="3" width="15.90625" style="8" customWidth="1"/>
+    <col min="4" max="6" width="13.7265625" customWidth="1"/>
+    <col min="7" max="7" width="17.453125" customWidth="1"/>
+    <col min="8" max="8" width="13.7265625" style="5" customWidth="1"/>
+    <col min="9" max="9" width="19.36328125" style="5" customWidth="1"/>
+    <col min="10" max="10" width="11.90625" customWidth="1"/>
+    <col min="11" max="13" width="13.7265625" customWidth="1"/>
+    <col min="14" max="14" width="17.453125" customWidth="1"/>
+    <col min="15" max="15" width="13.7265625" style="5" customWidth="1"/>
+    <col min="16" max="16" width="19.36328125" style="5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="24" customHeight="1">
@@ -595,9 +595,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="16.625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="16.6328125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
@@ -635,7 +635,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:1" ht="27">
+    <row r="8" spans="1:1" ht="28">
       <c r="A8" s="4" t="s">
         <v>22</v>
       </c>
@@ -645,7 +645,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:1" ht="27">
+    <row r="10" spans="1:1" ht="28">
       <c r="A10" s="4" t="s">
         <v>7</v>
       </c>
@@ -670,7 +670,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="15" spans="1:1" ht="27">
+    <row r="15" spans="1:1" ht="28">
       <c r="A15" s="4" t="s">
         <v>27</v>
       </c>
@@ -680,7 +680,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:1" ht="27">
+    <row r="17" spans="1:1" ht="28">
       <c r="A17" s="4" t="s">
         <v>14</v>
       </c>
@@ -695,7 +695,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <sheetData/>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/RepProdIndexGz.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/RepProdIndexGz.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\nyxp\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Git\NY\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="18530" windowHeight="7130"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="18525" windowHeight="7125"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -209,10 +209,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -520,19 +520,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:P1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="2" width="9.36328125" customWidth="1"/>
-    <col min="3" max="3" width="15.90625" style="8" customWidth="1"/>
-    <col min="4" max="6" width="13.7265625" customWidth="1"/>
-    <col min="7" max="7" width="17.453125" customWidth="1"/>
-    <col min="8" max="8" width="13.7265625" style="5" customWidth="1"/>
-    <col min="9" max="9" width="19.36328125" style="5" customWidth="1"/>
-    <col min="10" max="10" width="11.90625" customWidth="1"/>
-    <col min="11" max="13" width="13.7265625" customWidth="1"/>
-    <col min="14" max="14" width="17.453125" customWidth="1"/>
-    <col min="15" max="15" width="13.7265625" style="5" customWidth="1"/>
-    <col min="16" max="16" width="19.36328125" style="5" customWidth="1"/>
+    <col min="1" max="2" width="9.375" customWidth="1"/>
+    <col min="3" max="3" width="15.875" style="8" customWidth="1"/>
+    <col min="4" max="6" width="13.75" customWidth="1"/>
+    <col min="7" max="7" width="17.5" customWidth="1"/>
+    <col min="8" max="8" width="13.75" style="5" customWidth="1"/>
+    <col min="9" max="9" width="19.375" style="5" customWidth="1"/>
+    <col min="10" max="10" width="11.875" customWidth="1"/>
+    <col min="11" max="13" width="13.75" customWidth="1"/>
+    <col min="14" max="14" width="17.5" customWidth="1"/>
+    <col min="15" max="15" width="13.75" style="5" customWidth="1"/>
+    <col min="16" max="16" width="19.375" style="5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="24" customHeight="1">
@@ -595,9 +595,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="16.6328125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="16.625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
@@ -635,7 +635,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:1" ht="28">
+    <row r="8" spans="1:1" ht="27">
       <c r="A8" s="4" t="s">
         <v>22</v>
       </c>
@@ -645,7 +645,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:1" ht="28">
+    <row r="10" spans="1:1" ht="27">
       <c r="A10" s="4" t="s">
         <v>7</v>
       </c>
@@ -670,7 +670,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="15" spans="1:1" ht="28">
+    <row r="15" spans="1:1" ht="27">
       <c r="A15" s="4" t="s">
         <v>27</v>
       </c>
@@ -680,7 +680,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:1" ht="28">
+    <row r="17" spans="1:1" ht="27">
       <c r="A17" s="4" t="s">
         <v>14</v>
       </c>
@@ -695,7 +695,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/RepProdIndexGz.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/RepProdIndexGz.xlsx
@@ -107,7 +107,7 @@
     <t>母产品单位累计净值</t>
   </si>
   <si>
-    <t>日期(yyyy-mm-dd)*</t>
+    <t>日期(yyyy/mm/dd)*</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
